--- a/translations/welsh-translations/xlsx/23-producer-prns-accepted-selection.xlsx
+++ b/translations/welsh-translations/xlsx/23-producer-prns-accepted-selection.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="37">
   <si>
     <t>Translator notes</t>
   </si>
@@ -58,28 +58,22 @@
     <t>https://www.figma.com/design/T6jnQSPgRrAAYGSykX5Fca/Multi-year-and-Dec-Waste?node-id=1915-113629&amp;t=3WOTV5b531g8Cews-0</t>
   </si>
   <si>
+    <t>prns.acceptedSelection.tilesLabel</t>
+  </si>
+  <si>
+    <t>Accepted tonnage by material</t>
+  </si>
+  <si>
     <t>prns.acceptedSelection.heading</t>
   </si>
   <si>
     <t>You’ve accepted {{count}} PRNs and PERNs towards your {{year}} recycling obligations</t>
   </si>
   <si>
-    <t>prns.acceptedSelection.headingNoYear</t>
-  </si>
-  <si>
-    <t>You’ve accepted {{count}} PRNs and PERNs towards your recycling obligations</t>
-  </si>
-  <si>
     <t>prns.acceptedSelection.headingOne</t>
   </si>
   <si>
     <t>You’ve accepted 1 PRN or PERN towards your {{year}} recycling obligations</t>
-  </si>
-  <si>
-    <t>prns.acceptedSelection.headingOneNoYear</t>
-  </si>
-  <si>
-    <t>You’ve accepted 1 PRN or PERN towards your recycling obligations</t>
   </si>
   <si>
     <t>prns.acceptedSelection.tonnes</t>
@@ -526,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -817,28 +811,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:F18"/>
+  <autoFilter ref="A5:F17"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
